--- a/Assets/@Resources/Data/Excel/TravelData.xlsx
+++ b/Assets/@Resources/Data/Excel/TravelData.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,13 +519,11 @@
           <t>BreezingWindForest_Img</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>BTN_MAP_BREEZING_WIND_FOREST</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -541,7 +539,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BreezingWindForestEntranceText</t>
+          <t>BreezingWindForestDepth1Text</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -587,13 +585,11 @@
           <t>WhisperingCave_Img</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>BTN_MAP_WHISPERING_CAVE</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -609,7 +605,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WhisperingCaveEntranceText</t>
+          <t>WhisperingCaveDepth1Text</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -655,13 +651,11 @@
           <t>RuinedSanctum_Img</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>BTN_MAP_RUINED_SANCTUM</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -677,7 +671,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RuinedSanctumEntranceText</t>
+          <t>RuinedSanctumDepth1Text</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -698,6 +692,1032 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>BTN_STAGE_RUINED_SANCTUM_ENTRANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>21110</v>
+      </c>
+      <c r="B9" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth2Text</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>21120</v>
+      </c>
+      <c r="B10" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth3Text</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>21130</v>
+      </c>
+      <c r="B11" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth4Text</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>21140</v>
+      </c>
+      <c r="B12" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth5Text</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>21150</v>
+      </c>
+      <c r="B13" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth6Text</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>21160</v>
+      </c>
+      <c r="B14" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth7Text</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>21170</v>
+      </c>
+      <c r="B15" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth8Text</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D8</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21180</v>
+      </c>
+      <c r="B16" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth9Text</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D9</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21190</v>
+      </c>
+      <c r="B17" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BreezingWindForestDepth10Text</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFOREST_D10</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFOREST_D10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>22110</v>
+      </c>
+      <c r="B18" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth2Text</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>22120</v>
+      </c>
+      <c r="B19" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth3Text</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22130</v>
+      </c>
+      <c r="B20" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth4Text</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D4</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>22140</v>
+      </c>
+      <c r="B21" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth5Text</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>22150</v>
+      </c>
+      <c r="B22" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth6Text</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D6</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22160</v>
+      </c>
+      <c r="B23" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth7Text</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D7</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22170</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth8Text</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D8</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22180</v>
+      </c>
+      <c r="B25" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth9Text</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D9</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22190</v>
+      </c>
+      <c r="B26" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>WhisperingCaveDepth10Text</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVE_D10</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVE_D10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23110</v>
+      </c>
+      <c r="B27" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth2Text</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23120</v>
+      </c>
+      <c r="B28" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth3Text</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23130</v>
+      </c>
+      <c r="B29" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth4Text</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D4</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23140</v>
+      </c>
+      <c r="B30" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth5Text</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23150</v>
+      </c>
+      <c r="B31" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth6Text</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D6</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23160</v>
+      </c>
+      <c r="B32" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth7Text</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D7</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23170</v>
+      </c>
+      <c r="B33" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth8Text</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D8</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>23180</v>
+      </c>
+      <c r="B34" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth9Text</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D9</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>23190</v>
+      </c>
+      <c r="B35" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RuinedSanctumDepth10Text</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUM_D10</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUM_D10</t>
         </is>
       </c>
     </row>
@@ -712,7 +1732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +1808,627 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>21110</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>레벨 11 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>21120</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>레벨 21 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>21130</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>레벨 31 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>21140</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>레벨 41 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21150</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>51</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>레벨 51 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>21160</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>61</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>레벨 61 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>21170</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>71</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>레벨 71 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>21180</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>81</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>레벨 81 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>21190</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>91</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>레벨 91 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>22110</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>111</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>레벨 111 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>22120</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>121</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>레벨 121 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>22130</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>131</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>레벨 131 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>22140</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>141</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>레벨 141 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22150</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>151</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>레벨 151 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>22160</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>161</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>레벨 161 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>22170</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>171</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>레벨 171 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22180</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>181</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>레벨 181 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>22190</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>191</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>레벨 191 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23110</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>211</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>레벨 211 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23120</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>221</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>레벨 221 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23130</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>231</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>레벨 231 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23140</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>241</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>레벨 241 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23150</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>251</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>레벨 251 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23160</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>261</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>레벨 261 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23170</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>271</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>레벨 271 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23180</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>281</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>레벨 281 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23190</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>291</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>레벨 291 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/TravelData.xlsx
+++ b/Assets/@Resources/Data/Excel/TravelData.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PlaceNameTownAsdalText</t>
+          <t>PlaceAsdalText</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -499,139 +499,159 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21000</v>
+        <v>12000</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EXPLORE</t>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BreezingWindForestNameText</t>
+          <t>PlaceWindportText</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Img</t>
+          <t>Background_Village1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Village1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZING_WIND_FOREST</t>
+          <t>BTN_MAP_WINDPORT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>BTN_ENTER_WINDPORT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21100</v>
+        <v>13000</v>
       </c>
       <c r="B4" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EXPLORE</t>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth1Text</t>
+          <t>PlaceAshmineText</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
+          <t>Background_Village1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Battle</t>
+          <t>Village1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZING_WIND_FOREST_ENTRANCE</t>
+          <t>BTN_MAP_ASHMINE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BTN_STAGE_BREEZING_WIND_FOREST_ENTRANCE</t>
+          <t>BTN_ENTER_ASHMINE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EXPLORE</t>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WhisperingCaveNameText</t>
+          <t>PlaceFrostkeepText</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WhisperingCave_Img</t>
+          <t>Background_Village1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Village1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERING_CAVE</t>
+          <t>BTN_MAP_FROSTKEEP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>BTN_ENTER_FROSTKEEP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22100</v>
+        <v>15000</v>
       </c>
       <c r="B6" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EXPLORE</t>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth1Text</t>
+          <t>PlaceDawnspireText</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
+          <t>Background_Village1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Battle</t>
+          <t>Village1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERING_CAVE_ENTRANCE</t>
+          <t>BTN_MAP_DAWNSPIRE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BTN_STAGE_WHISPERING_CAVE_ENTRANCE</t>
+          <t>BTN_ENTER_DAWNSPIRE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>23000</v>
+        <v>21000</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -643,26 +663,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RuinedSanctumNameText</t>
+          <t>BreezingWindForestNameText</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Img</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINED_SANCTUM</t>
+          <t>BTN_MAP_BREEZINGWINDFOREST</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23100</v>
+        <v>21100</v>
       </c>
       <c r="B8" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -671,36 +691,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth1Text</t>
+          <t>WhisperingCaveNameText</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINED_SANCTUM_ENTRANCE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_RUINED_SANCTUM_ENTRANCE</t>
+          <t>BTN_MAP_WHISPERINGCAVE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21110</v>
+        <v>21200</v>
       </c>
       <c r="B9" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -709,36 +719,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth2Text</t>
+          <t>RuinedSanctumNameText</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D2</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D2</t>
+          <t>BTN_MAP_RUINEDSANCTUM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21120</v>
+        <v>21300</v>
       </c>
       <c r="B10" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -747,36 +747,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth3Text</t>
+          <t>SunkenGroveNameText</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D3</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D3</t>
+          <t>BTN_MAP_SUNKENGROVE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21130</v>
+        <v>21400</v>
       </c>
       <c r="B11" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -785,36 +775,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth4Text</t>
+          <t>HollowBurrowNameText</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D4</t>
+          <t>BTN_MAP_HOLLOWBURROW</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21140</v>
+        <v>22000</v>
       </c>
       <c r="B12" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -823,36 +803,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth5Text</t>
+          <t>SaltMarshNameText</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D5</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D5</t>
+          <t>BTN_MAP_SALTMARSH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>21150</v>
+        <v>22100</v>
       </c>
       <c r="B13" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -861,36 +831,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth6Text</t>
+          <t>TidalCavernNameText</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D6</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D6</t>
+          <t>BTN_MAP_TIDALCAVERN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21160</v>
+        <v>22200</v>
       </c>
       <c r="B14" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -899,36 +859,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth7Text</t>
+          <t>BrokenPierNameText</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D7</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D7</t>
+          <t>BTN_MAP_BROKENPIER</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21170</v>
+        <v>22300</v>
       </c>
       <c r="B15" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -937,36 +887,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth8Text</t>
+          <t>StormCliffNameText</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D8</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D8</t>
+          <t>BTN_MAP_STORMCLIFF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21180</v>
+        <v>22400</v>
       </c>
       <c r="B16" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -975,36 +915,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth9Text</t>
+          <t>DriftwoodWoodNameText</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D9</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D9</t>
+          <t>BTN_MAP_DRIFTWOODWOOD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>21190</v>
+        <v>23000</v>
       </c>
       <c r="B17" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1013,36 +943,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BreezingWindForestDepth10Text</t>
+          <t>CinderPitNameText</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BreezingWindForest_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BTN_MAP_BREEZINGWINDFOREST_D10</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_BREEZINGWINDFOREST_D10</t>
+          <t>BTN_MAP_CINDERPIT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22110</v>
+        <v>23100</v>
       </c>
       <c r="B18" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1051,36 +971,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth2Text</t>
+          <t>DeepShaftNameText</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D2</t>
+          <t>BTN_MAP_DEEPSHAFT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22120</v>
+        <v>23200</v>
       </c>
       <c r="B19" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1089,36 +999,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth3Text</t>
+          <t>RustHallNameText</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D3</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D3</t>
+          <t>BTN_MAP_RUSTHALL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22130</v>
+        <v>23300</v>
       </c>
       <c r="B20" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1127,36 +1027,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth4Text</t>
+          <t>EmberVeinNameText</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D4</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D4</t>
+          <t>BTN_MAP_EMBERVEIN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22140</v>
+        <v>23400</v>
       </c>
       <c r="B21" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1165,36 +1055,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth5Text</t>
+          <t>CollapsedTunnelNameText</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D5</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D5</t>
+          <t>BTN_MAP_COLLAPSEDTUNNEL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22150</v>
+        <v>24000</v>
       </c>
       <c r="B22" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1203,36 +1083,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth6Text</t>
+          <t>FrostWoodNameText</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D6</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D6</t>
+          <t>BTN_MAP_FROSTWOOD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22160</v>
+        <v>24100</v>
       </c>
       <c r="B23" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1241,36 +1111,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth7Text</t>
+          <t>GlacierCaveNameText</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D7</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D7</t>
+          <t>BTN_MAP_GLACIERCAVE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22170</v>
+        <v>24200</v>
       </c>
       <c r="B24" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1279,36 +1139,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth8Text</t>
+          <t>SilentChapelNameText</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D8</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D8</t>
+          <t>BTN_MAP_SILENTCHAPEL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22180</v>
+        <v>24300</v>
       </c>
       <c r="B25" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1317,36 +1167,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth9Text</t>
+          <t>WhiteWasteNameText</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D9</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D9</t>
+          <t>BTN_MAP_WHITEWASTE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22190</v>
+        <v>24400</v>
       </c>
       <c r="B26" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1355,36 +1195,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>WhisperingCaveDepth10Text</t>
+          <t>FrozenVaultNameText</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WhisperingCave_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BTN_MAP_WHISPERINGCAVE_D10</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_WHISPERINGCAVE_D10</t>
+          <t>BTN_MAP_FROZENVAULT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23110</v>
+        <v>25000</v>
       </c>
       <c r="B27" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1393,36 +1223,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth2Text</t>
+          <t>DawnGardenNameText</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D2</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D2</t>
+          <t>BTN_MAP_DAWNGARDEN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>23120</v>
+        <v>25100</v>
       </c>
       <c r="B28" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1431,36 +1251,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth3Text</t>
+          <t>VoidStairNameText</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D3</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D3</t>
+          <t>BTN_MAP_VOIDSTAIR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23130</v>
+        <v>25200</v>
       </c>
       <c r="B29" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1469,36 +1279,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth4Text</t>
+          <t>StarSanctumNameText</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>WhisperingCave_Img</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D4</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D4</t>
+          <t>BTN_MAP_STARSANCTUM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>23140</v>
+        <v>25300</v>
       </c>
       <c r="B30" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1507,36 +1307,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth5Text</t>
+          <t>LastRampartNameText</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>RuinedSanctum_Img</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D5</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D5</t>
+          <t>BTN_MAP_LASTRAMPART</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23150</v>
+        <v>25400</v>
       </c>
       <c r="B31" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1545,36 +1335,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth6Text</t>
+          <t>ThroneOfDawnNameText</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Battle</t>
+          <t>BreezingWindForest_Img</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D6</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D6</t>
+          <t>BTN_MAP_THRONEOFDAWN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>23160</v>
+        <v>21010</v>
       </c>
       <c r="B32" t="n">
-        <v>23000</v>
+        <v>21000</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1583,12 +1363,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth7Text</t>
+          <t>BreezingWindForestD1Text</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
+          <t>BreezingWindForest_Entry_Img</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1598,21 +1378,21 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D7</t>
+          <t>BTN_MAP_BREEZINGWINDFORESTD1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D7</t>
+          <t>BTN_STAGE_BREEZINGWINDFORESTD1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>23170</v>
+        <v>21020</v>
       </c>
       <c r="B33" t="n">
-        <v>23000</v>
+        <v>21000</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1621,12 +1401,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth8Text</t>
+          <t>BreezingWindForestD2Text</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
+          <t>BreezingWindForest_Entry_Img</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1636,21 +1416,21 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D8</t>
+          <t>BTN_MAP_BREEZINGWINDFORESTD2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D8</t>
+          <t>BTN_STAGE_BREEZINGWINDFORESTD2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>23180</v>
+        <v>21030</v>
       </c>
       <c r="B34" t="n">
-        <v>23000</v>
+        <v>21000</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1659,12 +1439,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RuinedSanctumDepth9Text</t>
+          <t>BreezingWindForestD3Text</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RuinedSanctum_Entry_Img</t>
+          <t>BreezingWindForest_Entry_Img</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1674,50 +1454,4648 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D9</t>
+          <t>BTN_MAP_BREEZINGWINDFORESTD3</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D9</t>
+          <t>BTN_STAGE_BREEZINGWINDFORESTD3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23190</v>
+        <v>21040</v>
       </c>
       <c r="B35" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BreezingWindForestD4Text</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFORESTD4</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFORESTD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>21050</v>
+      </c>
+      <c r="B36" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BreezingWindForestD5Text</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BREEZINGWINDFORESTD5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BREEZINGWINDFORESTD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21110</v>
+      </c>
+      <c r="B37" t="n">
+        <v>21100</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD1Text</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVED1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>21120</v>
+      </c>
+      <c r="B38" t="n">
+        <v>21100</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD2Text</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVED2</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVED2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>21130</v>
+      </c>
+      <c r="B39" t="n">
+        <v>21100</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD3Text</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVED3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVED3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>21140</v>
+      </c>
+      <c r="B40" t="n">
+        <v>21100</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD4Text</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVED4</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVED4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>21150</v>
+      </c>
+      <c r="B41" t="n">
+        <v>21100</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD5Text</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHISPERINGCAVED5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHISPERINGCAVED5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>21210</v>
+      </c>
+      <c r="B42" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD1Text</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUMD1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUMD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>21220</v>
+      </c>
+      <c r="B43" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD2Text</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUMD2</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUMD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>21230</v>
+      </c>
+      <c r="B44" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD3Text</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUMD3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>21240</v>
+      </c>
+      <c r="B45" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD4Text</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUMD4</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUMD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>21250</v>
+      </c>
+      <c r="B46" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD5Text</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUINEDSANCTUMD5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUINEDSANCTUMD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>21310</v>
+      </c>
+      <c r="B47" t="n">
+        <v>21300</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SunkenGroveD1Text</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SUNKENGROVED1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SUNKENGROVED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>21320</v>
+      </c>
+      <c r="B48" t="n">
+        <v>21300</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SunkenGroveD2Text</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SUNKENGROVED2</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SUNKENGROVED2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>21330</v>
+      </c>
+      <c r="B49" t="n">
+        <v>21300</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SunkenGroveD3Text</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SUNKENGROVED3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SUNKENGROVED3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>21340</v>
+      </c>
+      <c r="B50" t="n">
+        <v>21300</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SunkenGroveD4Text</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SUNKENGROVED4</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SUNKENGROVED4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>21350</v>
+      </c>
+      <c r="B51" t="n">
+        <v>21300</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SunkenGroveD5Text</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SUNKENGROVED5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SUNKENGROVED5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>21410</v>
+      </c>
+      <c r="B52" t="n">
+        <v>21400</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HollowBurrowD1Text</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>BTN_MAP_HOLLOWBURROWD1</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_HOLLOWBURROWD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>21420</v>
+      </c>
+      <c r="B53" t="n">
+        <v>21400</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HollowBurrowD2Text</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>BTN_MAP_HOLLOWBURROWD2</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_HOLLOWBURROWD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>21430</v>
+      </c>
+      <c r="B54" t="n">
+        <v>21400</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HollowBurrowD3Text</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>BTN_MAP_HOLLOWBURROWD3</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_HOLLOWBURROWD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>21440</v>
+      </c>
+      <c r="B55" t="n">
+        <v>21400</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HollowBurrowD4Text</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>BTN_MAP_HOLLOWBURROWD4</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_HOLLOWBURROWD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>21450</v>
+      </c>
+      <c r="B56" t="n">
+        <v>21400</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HollowBurrowD5Text</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BTN_MAP_HOLLOWBURROWD5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_HOLLOWBURROWD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>22010</v>
+      </c>
+      <c r="B57" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SaltMarshD1Text</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SALTMARSHD1</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SALTMARSHD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>22020</v>
+      </c>
+      <c r="B58" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SaltMarshD2Text</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SALTMARSHD2</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SALTMARSHD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22030</v>
+      </c>
+      <c r="B59" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SaltMarshD3Text</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SALTMARSHD3</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SALTMARSHD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>22040</v>
+      </c>
+      <c r="B60" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SaltMarshD4Text</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SALTMARSHD4</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SALTMARSHD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>22050</v>
+      </c>
+      <c r="B61" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SaltMarshD5Text</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SALTMARSHD5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SALTMARSHD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>22110</v>
+      </c>
+      <c r="B62" t="n">
+        <v>22100</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TidalCavernD1Text</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>BTN_MAP_TIDALCAVERND1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_TIDALCAVERND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>22120</v>
+      </c>
+      <c r="B63" t="n">
+        <v>22100</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TidalCavernD2Text</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>BTN_MAP_TIDALCAVERND2</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_TIDALCAVERND2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>22130</v>
+      </c>
+      <c r="B64" t="n">
+        <v>22100</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TidalCavernD3Text</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>BTN_MAP_TIDALCAVERND3</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_TIDALCAVERND3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>22140</v>
+      </c>
+      <c r="B65" t="n">
+        <v>22100</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TidalCavernD4Text</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>BTN_MAP_TIDALCAVERND4</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_TIDALCAVERND4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>22150</v>
+      </c>
+      <c r="B66" t="n">
+        <v>22100</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TidalCavernD5Text</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>BTN_MAP_TIDALCAVERND5</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_TIDALCAVERND5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>22210</v>
+      </c>
+      <c r="B67" t="n">
+        <v>22200</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BrokenPierD1Text</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BROKENPIERD1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BROKENPIERD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>22220</v>
+      </c>
+      <c r="B68" t="n">
+        <v>22200</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BrokenPierD2Text</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BROKENPIERD2</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BROKENPIERD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>22230</v>
+      </c>
+      <c r="B69" t="n">
+        <v>22200</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BrokenPierD3Text</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BROKENPIERD3</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BROKENPIERD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>22240</v>
+      </c>
+      <c r="B70" t="n">
+        <v>22200</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BrokenPierD4Text</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BROKENPIERD4</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BROKENPIERD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>22250</v>
+      </c>
+      <c r="B71" t="n">
+        <v>22200</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BrokenPierD5Text</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>BTN_MAP_BROKENPIERD5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_BROKENPIERD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>22310</v>
+      </c>
+      <c r="B72" t="n">
+        <v>22300</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>StormCliffD1Text</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STORMCLIFFD1</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STORMCLIFFD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>22320</v>
+      </c>
+      <c r="B73" t="n">
+        <v>22300</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>StormCliffD2Text</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STORMCLIFFD2</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STORMCLIFFD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>22330</v>
+      </c>
+      <c r="B74" t="n">
+        <v>22300</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>StormCliffD3Text</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STORMCLIFFD3</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STORMCLIFFD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>22340</v>
+      </c>
+      <c r="B75" t="n">
+        <v>22300</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>StormCliffD4Text</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STORMCLIFFD4</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STORMCLIFFD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>22350</v>
+      </c>
+      <c r="B76" t="n">
+        <v>22300</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>StormCliffD5Text</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STORMCLIFFD5</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STORMCLIFFD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>22410</v>
+      </c>
+      <c r="B77" t="n">
+        <v>22400</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD1Text</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DRIFTWOODWOODD1</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DRIFTWOODWOODD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>22420</v>
+      </c>
+      <c r="B78" t="n">
+        <v>22400</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD2Text</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DRIFTWOODWOODD2</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DRIFTWOODWOODD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>22430</v>
+      </c>
+      <c r="B79" t="n">
+        <v>22400</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD3Text</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DRIFTWOODWOODD3</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DRIFTWOODWOODD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>22440</v>
+      </c>
+      <c r="B80" t="n">
+        <v>22400</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD4Text</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DRIFTWOODWOODD4</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DRIFTWOODWOODD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>22450</v>
+      </c>
+      <c r="B81" t="n">
+        <v>22400</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD5Text</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DRIFTWOODWOODD5</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DRIFTWOODWOODD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>23010</v>
+      </c>
+      <c r="B82" t="n">
         <v>23000</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>EXPLORE</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>RuinedSanctumDepth10Text</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CinderPitD1Text</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>BTN_MAP_CINDERPITD1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_CINDERPITD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>23020</v>
+      </c>
+      <c r="B83" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CinderPitD2Text</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>BTN_MAP_CINDERPITD2</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_CINDERPITD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>23030</v>
+      </c>
+      <c r="B84" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CinderPitD3Text</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>BTN_MAP_CINDERPITD3</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_CINDERPITD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>23040</v>
+      </c>
+      <c r="B85" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CinderPitD4Text</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>BTN_MAP_CINDERPITD4</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_CINDERPITD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>23050</v>
+      </c>
+      <c r="B86" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CinderPitD5Text</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>BTN_MAP_CINDERPITD5</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_CINDERPITD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>23110</v>
+      </c>
+      <c r="B87" t="n">
+        <v>23100</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DeepShaftD1Text</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>RuinedSanctum_Entry_Img</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Battle</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BTN_MAP_RUINEDSANCTUM_D10</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>BTN_STAGE_RUINEDSANCTUM_D10</t>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DEEPSHAFTD1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DEEPSHAFTD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>23120</v>
+      </c>
+      <c r="B88" t="n">
+        <v>23100</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DeepShaftD2Text</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DEEPSHAFTD2</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DEEPSHAFTD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>23130</v>
+      </c>
+      <c r="B89" t="n">
+        <v>23100</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>DeepShaftD3Text</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DEEPSHAFTD3</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DEEPSHAFTD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>23140</v>
+      </c>
+      <c r="B90" t="n">
+        <v>23100</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DeepShaftD4Text</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DEEPSHAFTD4</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DEEPSHAFTD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>23150</v>
+      </c>
+      <c r="B91" t="n">
+        <v>23100</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DeepShaftD5Text</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DEEPSHAFTD5</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DEEPSHAFTD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>23210</v>
+      </c>
+      <c r="B92" t="n">
+        <v>23200</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>RustHallD1Text</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUSTHALLD1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUSTHALLD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>23220</v>
+      </c>
+      <c r="B93" t="n">
+        <v>23200</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>RustHallD2Text</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUSTHALLD2</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUSTHALLD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>23230</v>
+      </c>
+      <c r="B94" t="n">
+        <v>23200</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>RustHallD3Text</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUSTHALLD3</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUSTHALLD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>23240</v>
+      </c>
+      <c r="B95" t="n">
+        <v>23200</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RustHallD4Text</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUSTHALLD4</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUSTHALLD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>23250</v>
+      </c>
+      <c r="B96" t="n">
+        <v>23200</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>RustHallD5Text</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>BTN_MAP_RUSTHALLD5</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_RUSTHALLD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>23310</v>
+      </c>
+      <c r="B97" t="n">
+        <v>23300</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EmberVeinD1Text</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>BTN_MAP_EMBERVEIND1</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_EMBERVEIND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>23320</v>
+      </c>
+      <c r="B98" t="n">
+        <v>23300</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EmberVeinD2Text</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>BTN_MAP_EMBERVEIND2</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_EMBERVEIND2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>23330</v>
+      </c>
+      <c r="B99" t="n">
+        <v>23300</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EmberVeinD3Text</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>BTN_MAP_EMBERVEIND3</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_EMBERVEIND3</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>23340</v>
+      </c>
+      <c r="B100" t="n">
+        <v>23300</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EmberVeinD4Text</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>BTN_MAP_EMBERVEIND4</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_EMBERVEIND4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>23350</v>
+      </c>
+      <c r="B101" t="n">
+        <v>23300</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>EmberVeinD5Text</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>BTN_MAP_EMBERVEIND5</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_EMBERVEIND5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>23410</v>
+      </c>
+      <c r="B102" t="n">
+        <v>23400</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD1Text</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>BTN_MAP_COLLAPSEDTUNNELD1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_COLLAPSEDTUNNELD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>23420</v>
+      </c>
+      <c r="B103" t="n">
+        <v>23400</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD2Text</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>BTN_MAP_COLLAPSEDTUNNELD2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_COLLAPSEDTUNNELD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>23430</v>
+      </c>
+      <c r="B104" t="n">
+        <v>23400</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD3Text</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>BTN_MAP_COLLAPSEDTUNNELD3</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_COLLAPSEDTUNNELD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>23440</v>
+      </c>
+      <c r="B105" t="n">
+        <v>23400</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD4Text</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>BTN_MAP_COLLAPSEDTUNNELD4</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_COLLAPSEDTUNNELD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>23450</v>
+      </c>
+      <c r="B106" t="n">
+        <v>23400</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD5Text</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>BTN_MAP_COLLAPSEDTUNNELD5</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_COLLAPSEDTUNNELD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>24010</v>
+      </c>
+      <c r="B107" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>FrostWoodD1Text</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROSTWOODD1</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROSTWOODD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>24020</v>
+      </c>
+      <c r="B108" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>FrostWoodD2Text</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROSTWOODD2</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROSTWOODD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>24030</v>
+      </c>
+      <c r="B109" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>FrostWoodD3Text</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROSTWOODD3</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROSTWOODD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>24040</v>
+      </c>
+      <c r="B110" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>FrostWoodD4Text</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROSTWOODD4</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROSTWOODD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>24050</v>
+      </c>
+      <c r="B111" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>FrostWoodD5Text</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROSTWOODD5</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROSTWOODD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>24110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>24100</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GlacierCaveD1Text</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>BTN_MAP_GLACIERCAVED1</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_GLACIERCAVED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>24120</v>
+      </c>
+      <c r="B113" t="n">
+        <v>24100</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GlacierCaveD2Text</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>BTN_MAP_GLACIERCAVED2</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_GLACIERCAVED2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>24130</v>
+      </c>
+      <c r="B114" t="n">
+        <v>24100</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>GlacierCaveD3Text</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>BTN_MAP_GLACIERCAVED3</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_GLACIERCAVED3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>24140</v>
+      </c>
+      <c r="B115" t="n">
+        <v>24100</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>GlacierCaveD4Text</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>BTN_MAP_GLACIERCAVED4</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_GLACIERCAVED4</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>24150</v>
+      </c>
+      <c r="B116" t="n">
+        <v>24100</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>GlacierCaveD5Text</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>BTN_MAP_GLACIERCAVED5</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_GLACIERCAVED5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>24210</v>
+      </c>
+      <c r="B117" t="n">
+        <v>24200</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SilentChapelD1Text</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SILENTCHAPELD1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SILENTCHAPELD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>24220</v>
+      </c>
+      <c r="B118" t="n">
+        <v>24200</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SilentChapelD2Text</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SILENTCHAPELD2</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SILENTCHAPELD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>24230</v>
+      </c>
+      <c r="B119" t="n">
+        <v>24200</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SilentChapelD3Text</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SILENTCHAPELD3</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SILENTCHAPELD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>24240</v>
+      </c>
+      <c r="B120" t="n">
+        <v>24200</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SilentChapelD4Text</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SILENTCHAPELD4</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SILENTCHAPELD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>24250</v>
+      </c>
+      <c r="B121" t="n">
+        <v>24200</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SilentChapelD5Text</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>BTN_MAP_SILENTCHAPELD5</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_SILENTCHAPELD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>24310</v>
+      </c>
+      <c r="B122" t="n">
+        <v>24300</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>WhiteWasteD1Text</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHITEWASTED1</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHITEWASTED1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>24320</v>
+      </c>
+      <c r="B123" t="n">
+        <v>24300</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>WhiteWasteD2Text</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHITEWASTED2</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHITEWASTED2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>24330</v>
+      </c>
+      <c r="B124" t="n">
+        <v>24300</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>WhiteWasteD3Text</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHITEWASTED3</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHITEWASTED3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>24340</v>
+      </c>
+      <c r="B125" t="n">
+        <v>24300</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>WhiteWasteD4Text</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHITEWASTED4</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHITEWASTED4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>24350</v>
+      </c>
+      <c r="B126" t="n">
+        <v>24300</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>WhiteWasteD5Text</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>BTN_MAP_WHITEWASTED5</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_WHITEWASTED5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>24410</v>
+      </c>
+      <c r="B127" t="n">
+        <v>24400</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>FrozenVaultD1Text</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROZENVAULTD1</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROZENVAULTD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>24420</v>
+      </c>
+      <c r="B128" t="n">
+        <v>24400</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>FrozenVaultD2Text</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROZENVAULTD2</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROZENVAULTD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>24430</v>
+      </c>
+      <c r="B129" t="n">
+        <v>24400</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>FrozenVaultD3Text</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROZENVAULTD3</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROZENVAULTD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>24440</v>
+      </c>
+      <c r="B130" t="n">
+        <v>24400</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>FrozenVaultD4Text</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROZENVAULTD4</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROZENVAULTD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>24450</v>
+      </c>
+      <c r="B131" t="n">
+        <v>24400</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>FrozenVaultD5Text</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>BTN_MAP_FROZENVAULTD5</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_FROZENVAULTD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>25010</v>
+      </c>
+      <c r="B132" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DawnGardenD1Text</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DAWNGARDEND1</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DAWNGARDEND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>25020</v>
+      </c>
+      <c r="B133" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DawnGardenD2Text</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DAWNGARDEND2</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DAWNGARDEND2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>25030</v>
+      </c>
+      <c r="B134" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DawnGardenD3Text</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DAWNGARDEND3</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DAWNGARDEND3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>25040</v>
+      </c>
+      <c r="B135" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DawnGardenD4Text</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DAWNGARDEND4</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DAWNGARDEND4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>25050</v>
+      </c>
+      <c r="B136" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DawnGardenD5Text</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>BTN_MAP_DAWNGARDEND5</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_DAWNGARDEND5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>25110</v>
+      </c>
+      <c r="B137" t="n">
+        <v>25100</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VoidStairD1Text</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>BTN_MAP_VOIDSTAIRD1</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_VOIDSTAIRD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>25120</v>
+      </c>
+      <c r="B138" t="n">
+        <v>25100</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VoidStairD2Text</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>BTN_MAP_VOIDSTAIRD2</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_VOIDSTAIRD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>25130</v>
+      </c>
+      <c r="B139" t="n">
+        <v>25100</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VoidStairD3Text</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>BTN_MAP_VOIDSTAIRD3</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_VOIDSTAIRD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>25140</v>
+      </c>
+      <c r="B140" t="n">
+        <v>25100</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VoidStairD4Text</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>BTN_MAP_VOIDSTAIRD4</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_VOIDSTAIRD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>25150</v>
+      </c>
+      <c r="B141" t="n">
+        <v>25100</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VoidStairD5Text</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>BTN_MAP_VOIDSTAIRD5</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_VOIDSTAIRD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>25210</v>
+      </c>
+      <c r="B142" t="n">
+        <v>25200</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>StarSanctumD1Text</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STARSANCTUMD1</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STARSANCTUMD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>25220</v>
+      </c>
+      <c r="B143" t="n">
+        <v>25200</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>StarSanctumD2Text</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STARSANCTUMD2</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STARSANCTUMD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>25230</v>
+      </c>
+      <c r="B144" t="n">
+        <v>25200</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>StarSanctumD3Text</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STARSANCTUMD3</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STARSANCTUMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25240</v>
+      </c>
+      <c r="B145" t="n">
+        <v>25200</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>StarSanctumD4Text</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STARSANCTUMD4</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STARSANCTUMD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>25250</v>
+      </c>
+      <c r="B146" t="n">
+        <v>25200</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>StarSanctumD5Text</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>WhisperingCave_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>BTN_MAP_STARSANCTUMD5</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_STARSANCTUMD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>25310</v>
+      </c>
+      <c r="B147" t="n">
+        <v>25300</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LastRampartD1Text</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>BTN_MAP_LASTRAMPARTD1</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_LASTRAMPARTD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>25320</v>
+      </c>
+      <c r="B148" t="n">
+        <v>25300</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LastRampartD2Text</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>BTN_MAP_LASTRAMPARTD2</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_LASTRAMPARTD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>25330</v>
+      </c>
+      <c r="B149" t="n">
+        <v>25300</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LastRampartD3Text</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>BTN_MAP_LASTRAMPARTD3</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_LASTRAMPARTD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>25340</v>
+      </c>
+      <c r="B150" t="n">
+        <v>25300</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LastRampartD4Text</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>BTN_MAP_LASTRAMPARTD4</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_LASTRAMPARTD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>25350</v>
+      </c>
+      <c r="B151" t="n">
+        <v>25300</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LastRampartD5Text</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RuinedSanctum_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>BTN_MAP_LASTRAMPARTD5</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_LASTRAMPARTD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>25410</v>
+      </c>
+      <c r="B152" t="n">
+        <v>25400</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD1Text</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>BTN_MAP_THRONEOFDAWND1</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_THRONEOFDAWND1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>25420</v>
+      </c>
+      <c r="B153" t="n">
+        <v>25400</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD2Text</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>BTN_MAP_THRONEOFDAWND2</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_THRONEOFDAWND2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>25430</v>
+      </c>
+      <c r="B154" t="n">
+        <v>25400</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD3Text</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>BTN_MAP_THRONEOFDAWND3</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_THRONEOFDAWND3</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>25440</v>
+      </c>
+      <c r="B155" t="n">
+        <v>25400</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD4Text</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>BTN_MAP_THRONEOFDAWND4</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_THRONEOFDAWND4</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>25450</v>
+      </c>
+      <c r="B156" t="n">
+        <v>25400</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>EXPLORE</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD5Text</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>BreezingWindForest_Entry_Img</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>BTN_MAP_THRONEOFDAWND5</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>BTN_STAGE_THRONEOFDAWND5</t>
         </is>
       </c>
     </row>
@@ -1732,7 +6110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1764,53 +6142,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22000</v>
+        <v>21100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QUEST_CLEAR</t>
+          <t>LEVEL_REQUIRED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2급 모험가 승급 후 개방됩니다.</t>
+          <t>레벨 13 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>23000</v>
+        <v>21200</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QUEST_CLEAR</t>
+          <t>LEVEL_REQUIRED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>아직 개방되지 않은 지역입니다.</t>
+          <t>레벨 25 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21110</v>
+        <v>21300</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1819,21 +6197,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>레벨 11 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 37 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21120</v>
+        <v>21400</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1842,21 +6220,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>레벨 21 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 49 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21130</v>
+        <v>22000</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1865,21 +6243,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>레벨 31 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 61 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21140</v>
+        <v>22100</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1888,21 +6266,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>레벨 41 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 73 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21150</v>
+        <v>22200</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1911,21 +6289,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>레벨 51 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 85 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21160</v>
+        <v>22300</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1934,21 +6312,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>레벨 61 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 97 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21170</v>
+        <v>22400</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1957,21 +6335,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>레벨 71 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 109 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21180</v>
+        <v>23000</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1980,21 +6358,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>121</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>레벨 81 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 121 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21190</v>
+        <v>23100</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2003,21 +6381,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>레벨 91 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 133 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22110</v>
+        <v>23200</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2026,21 +6404,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>145</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>레벨 111 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 145 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22120</v>
+        <v>23300</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2049,21 +6427,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>157</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>레벨 121 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 157 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22130</v>
+        <v>23400</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2072,21 +6450,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>레벨 131 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 169 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22140</v>
+        <v>24000</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2095,21 +6473,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>181</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>레벨 141 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 181 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22150</v>
+        <v>24100</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2118,21 +6496,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>193</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>레벨 151 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 193 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22160</v>
+        <v>24200</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2141,21 +6519,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>205</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>레벨 161 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 205 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22170</v>
+        <v>24300</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2164,21 +6542,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>레벨 171 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 217 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22180</v>
+        <v>24400</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2187,21 +6565,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>레벨 181 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 229 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22190</v>
+        <v>25000</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2210,21 +6588,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>레벨 191 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 241 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23110</v>
+        <v>25100</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2233,21 +6611,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>레벨 211 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 253 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23120</v>
+        <v>25200</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2256,21 +6634,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>265</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>레벨 221 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 265 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23130</v>
+        <v>25300</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2279,21 +6657,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>277</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>레벨 231 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 277 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23140</v>
+        <v>25400</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2302,21 +6680,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>289</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>레벨 241 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 289 이상이어야 갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23150</v>
+        <v>21020</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2325,21 +6703,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>251</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>레벨 251 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 3 이상이어야 들어갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23160</v>
+        <v>21030</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2348,21 +6726,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>261</v>
+        <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>레벨 261 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 5 이상이어야 들어갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>23170</v>
+        <v>21040</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2371,21 +6749,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>271</v>
+        <v>8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>레벨 271 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 8 이상이어야 들어갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23180</v>
+        <v>21050</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2394,21 +6772,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>281</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>레벨 281 이상이어야 들어갈 수 있습니다.</t>
+          <t>레벨 10 이상이어야 들어갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>23190</v>
+        <v>21110</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2417,15 +6795,2752 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>레벨 13 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>21120</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>레벨 15 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>21130</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>17</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>레벨 17 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>21140</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>레벨 20 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>21150</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>22</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>레벨 22 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>21210</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>레벨 25 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>21220</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>27</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>레벨 27 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21230</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>29</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>레벨 29 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>21240</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>32</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>레벨 32 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>21250</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>34</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>레벨 34 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>21310</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>37</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>레벨 37 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>21320</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>39</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>레벨 39 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>21330</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>41</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>레벨 41 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>21340</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>44</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>레벨 44 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>21350</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>46</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>레벨 46 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>21410</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>49</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>레벨 49 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>21420</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>51</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>레벨 51 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>21430</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>53</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>레벨 53 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>21440</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>56</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>레벨 56 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>21450</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>58</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>레벨 58 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>22010</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>61</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>레벨 61 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>22020</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>63</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>레벨 63 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>22030</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>65</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>레벨 65 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>22040</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>68</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>레벨 68 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>22050</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>70</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>레벨 70 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>22110</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>73</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>레벨 73 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>22120</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>75</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>레벨 75 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>22130</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>77</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>레벨 77 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>22140</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>80</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>레벨 80 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22150</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>82</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>레벨 82 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>22210</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>85</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>레벨 85 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>22220</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>87</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>레벨 87 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>22230</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>89</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>레벨 89 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>22240</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>92</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>레벨 92 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>22250</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>94</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>레벨 94 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>22310</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>97</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>레벨 97 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>22320</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>99</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>레벨 99 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>22330</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>101</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>레벨 101 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>22340</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>104</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>레벨 104 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>22350</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>106</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>레벨 106 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>22410</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>109</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>레벨 109 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>22420</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>111</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>레벨 111 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>22430</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>113</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>레벨 113 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>22440</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>116</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>레벨 116 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>22450</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>118</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>레벨 118 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>23010</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>121</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>레벨 121 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>23020</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>123</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>레벨 123 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>23030</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>125</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>레벨 125 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>23040</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>128</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>레벨 128 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>23050</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>130</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>레벨 130 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>23110</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>133</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>레벨 133 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>23120</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>135</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>레벨 135 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>23130</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>137</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>레벨 137 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>23140</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>레벨 140 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>23150</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>142</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>레벨 142 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>23210</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>145</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>레벨 145 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>23220</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>147</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>레벨 147 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>23230</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>149</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>레벨 149 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>23240</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>152</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>레벨 152 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>23250</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>154</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>레벨 154 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>23310</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>157</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>레벨 157 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>23320</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>159</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>레벨 159 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>23330</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>161</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>레벨 161 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>23340</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>164</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>레벨 164 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>23350</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>166</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>레벨 166 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>23410</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>169</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>레벨 169 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>23420</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>171</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>레벨 171 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>23430</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>173</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>레벨 173 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>23440</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>176</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>레벨 176 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>23450</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>178</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>레벨 178 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>24010</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>181</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>레벨 181 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>24020</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>183</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>레벨 183 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>24030</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>185</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>레벨 185 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>24040</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>188</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>레벨 188 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>24050</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>190</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>레벨 190 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>24110</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>193</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>레벨 193 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>24120</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>195</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>레벨 195 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>24130</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>197</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>레벨 197 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>24140</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>200</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>레벨 200 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>24150</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>202</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>레벨 202 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>24210</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>205</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>레벨 205 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>24220</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>207</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>레벨 207 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>24230</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>209</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>레벨 209 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>24240</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>212</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>레벨 212 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>24250</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>214</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>레벨 214 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>24310</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>217</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>레벨 217 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>24320</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>219</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>레벨 219 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>24330</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>221</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>레벨 221 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>24340</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>224</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>레벨 224 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>24350</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>226</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>레벨 226 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>24410</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>229</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>레벨 229 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>24420</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>231</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>레벨 231 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>24430</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>233</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>레벨 233 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>24440</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>236</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>레벨 236 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>24450</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>238</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>레벨 238 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>25010</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>241</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>레벨 241 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>25020</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>243</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>레벨 243 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>25030</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>245</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>레벨 245 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>25040</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>248</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>레벨 248 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>25050</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>250</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>레벨 250 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>25110</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>253</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>레벨 253 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>25120</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>255</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>레벨 255 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>25130</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>257</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>레벨 257 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>25140</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>260</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>레벨 260 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>25150</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>262</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>레벨 262 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>25210</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>265</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>레벨 265 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>25220</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>267</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>레벨 267 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>25230</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>269</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>레벨 269 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>25240</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>272</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>레벨 272 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>25250</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>274</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>레벨 274 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>25310</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>277</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>레벨 277 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>25320</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>279</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>레벨 279 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>25330</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>281</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>레벨 281 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>25340</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>284</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>레벨 284 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>25350</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>286</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>레벨 286 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25410</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>289</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>레벨 289 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>25420</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D146" t="n">
         <v>291</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>레벨 291 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>25430</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>293</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>레벨 293 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>25440</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>296</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>레벨 296 이상이어야 들어갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>25450</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>LEVEL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>298</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>레벨 298 이상이어야 들어갈 수 있습니다.</t>
         </is>
       </c>
     </row>
